--- a/MPe_V6_WORK/MPeV6PCB/MPeV6PCB/BOM/MPeV6PCB_BOM.xlsx
+++ b/MPe_V6_WORK/MPeV6PCB/MPeV6PCB/BOM/MPeV6PCB_BOM.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BOMTable" displayName="BOMTable" ref="A1:F41" headerRowCount="1">
-  <autoFilter ref="A1:F41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BOMTable" displayName="BOMTable" ref="A1:F43" headerRowCount="1">
+  <autoFilter ref="A1:F43"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Designator"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R9,R12</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R10,R11,R24,R27,R28,R30,R37,R38</t>
+          <t>R9,R12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R13,R14</t>
+          <t>R10,R11,R28,R30,R37,R38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75k</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R13,R14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4k7</t>
+          <t>75k</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.2K</t>
+          <t>4k7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SCR1</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SamacSys_Parts:DG30825403P1400AH</t>
+          <t>Resistor_SMD:R_0805_2012Metric_Pad1.20x1.40mm_HandSolder</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JP7</t>
+          <t>2.2K</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SCR2</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SamacSys_Parts:DG30825403P1400AH</t>
+          <t>Resistor_SMD:R_0805_2012Metric_Pad1.20x1.40mm_HandSolder</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>JP8</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SPD/TOT1</t>
+          <t>SCR1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JP9</t>
+          <t>JP7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1301,22 +1301,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SW1,SW2</t>
+          <t>SCR2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Button_Switch_THT:SW_DIP_SPSTx02_Slide_9.78x7.26mm_W7.62mm_P2.54mm</t>
+          <t>SamacSys_Parts:DG30825403P1400AH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SW_DIP_x02</t>
+          <t>JP8</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SW3</t>
+          <t>SPD/TOT1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SamacSys_Parts:DG30825402P1400AH</t>
+          <t>SamacSys_Parts:DG30825403P1400AH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>JP9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TIN1</t>
+          <t>SW1,SW2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SamacSys_Parts:DG30825403P1400AH</t>
+          <t>Button_Switch_THT:SW_DIP_SPSTx02_Slide_9.78x7.26mm_W7.62mm_P2.54mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>J10</t>
+          <t>SW_DIP_x02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>SW3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New_Library_Footprint:ADS1115PCB</t>
+          <t>SamacSys_Parts:DG30825402P1400AH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>~</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>TIN1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New_Library_Footprint:12V Step-Down</t>
+          <t>SamacSys_Parts:DG30825403P1400AH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Step-down 12V</t>
+          <t>J10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New_Library_Footprint:5V Step-Down</t>
+          <t>New_Library_Footprint:ADS1115PCB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Step-down 5V</t>
+          <t>~</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UART1</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SamacSys_Parts:DG30825402P1400AH</t>
+          <t>New_Library_Footprint:12V Step-Down</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>JP2</t>
+          <t>Step-down 12V</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1483,25 +1483,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New_Library_Footprint:5V Step-Down</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Step-down 5V</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UART1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SamacSys_Parts:DG30825402P1400AH</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>JP2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>VIN1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>SamacSys_Parts:DG30825403P1400AH</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>JP5</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
